--- a/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
+++ b/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
@@ -108,15 +108,15 @@
     <t xml:space="preserve">Clicked on "Send Offer" button on "Queuing Cargo" board</t>
   </si>
   <si>
+    <t xml:space="preserve">Please fill in all required data. After you click "Submit Offer" Buyer will be notified. Weight on Buyer's order is subject to final reweighing.</t>
+  </si>
+  <si>
     <t xml:space="preserve">A carrier is selecting your order. Wait for carrier to offer shipment cost.</t>
   </si>
   <si>
     <t xml:space="preserve">A carrier is selecting Buyer's Order. Waiting for Carrier to offer shipment cost.</t>
   </si>
   <si>
-    <t xml:space="preserve">Please fill in all required data. After you click "Submit Offer" Buyer will be notified. Weight on Buyer's order is subject to final reweighing.</t>
-  </si>
-  <si>
     <t>4.2</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t>5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">You accept the shipment cost, please pay the first deposit</t>
+    <t xml:space="preserve">You accept the shipment cost, please pay the first deposit.</t>
   </si>
   <si>
     <t xml:space="preserve">Buyer accepted the shipment cost. Waiting for the Buyer's deposit and admin fund verification before make purchases.</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Clicked on "Submit Transfer Proof"</t>
   </si>
   <si>
-    <t xml:space="preserve">Transfer proof submitted. Waiting for Admin fund verification</t>
+    <t xml:space="preserve">Transfer proof submitted. Waiting for Admin fund verification.</t>
   </si>
   <si>
     <t xml:space="preserve">Buyer submitted transfer proof. Waiting for Admin fund verification.</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Your deposit verified. Please use the Chat Box to chat with Proxy Buyer regarding any changing on product specification, if any..</t>
   </si>
   <si>
-    <t xml:space="preserve">Buyer's deposit verified. You can start buying the products, prepare the package (box or luggage), then select "Finalizing Order" button. Use Chat Box to chat with Buyer if there is any issues regarding the order specifications (changes of size, color, type, quantity; out-of-stock; price increase, substituted, etc.)</t>
+    <t xml:space="preserve">Buyer's deposit verified. You can start buying the products, prepare the package (box or luggage), then select "Finalizing Order" button. Use Chat Box to chat with Buyer if there is any issues regarding the order specifications (changes of size, color, type, quantity; out-of-stock; price increase, substituted, etc.).</t>
   </si>
   <si>
     <t xml:space="preserve">Buyer's deposit verified. Waiting  for Proxy Buyer to Finalize the Order.</t>
@@ -180,15 +180,9 @@
     <t xml:space="preserve">Clicked on "Finalizing Order"</t>
   </si>
   <si>
-    <t xml:space="preserve">Proxy Buyer about finalizing your order. Please make sure you have provide consents on any product specification discrepancies on the Chat Box message, if any.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Please fill in all Actual Quantity and Unit Cost, Final Total Weight, upload Products photos, upload Box/Luggage photo before it closed. Gather and inserting all products receipts to an envelope, sealed it and put it inside the box/luggage. Please make sure you have Buyer's consent on any product specifications discrepancies, if any. Then select "Mark Package Ready".</t>
   </si>
   <si>
-    <t xml:space="preserve">Proxy Buyer is Finalizing the Order. Waiting  for Proxy Buyer Marking Package is Ready.</t>
-  </si>
-  <si>
     <t>6.2</t>
   </si>
   <si>
@@ -225,19 +219,23 @@
     <t xml:space="preserve">Clicked on "View" action button on "Action" column on "My Travel Plan" table.</t>
   </si>
   <si>
+    <t xml:space="preserve">Please fill in the Customs Duty amount and click "Send Duty Amount". Do not pay the Duty until you are notified that the Buyer has paid the deposit and the funds have been verified by Admin.</t>
+  </si>
+  <si>
     <t>8.2</t>
   </si>
   <si>
     <t xml:space="preserve">Clicked on "Send Duty Amount"</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrier has arrived. Please make deposit for Customs Duty payment, Products Cost shoratge and Shipment Cost shortage, if any.</t>
+    <t xml:space="preserve">Your package has arrived.
+Please pay the unpaid balance of IDR &lt;calculated&gt; &lt;(Ccy &lt;calculated&gt; @ &lt;current fx rate&gt;) to:</t>
   </si>
   <si>
     <t xml:space="preserve">Carrier has arrived. Your payout will be disbursed after Buyer receive the package.</t>
   </si>
   <si>
-    <t xml:space="preserve">Duty amount sent, waiting for Buyer's deposit and fund verification. Once verified you can pay the Duty and upload the Actual Proof.</t>
+    <t xml:space="preserve">Duty amount sent, waiting for Buyer's deposit and fund verification. Once verified you can pay the Duty and upload the receipt.</t>
   </si>
   <si>
     <t>9.1</t>
@@ -273,16 +271,16 @@
     <t xml:space="preserve">Clicked on "Upload Receipt"</t>
   </si>
   <si>
-    <t xml:space="preserve">Customs Duty paid. Please fill in your prefered courier nama and type (regular, express, etc.)</t>
+    <t xml:space="preserve">Customs Duty paid. Please fill in your prefered courier name and type (regular, express, etc.)</t>
   </si>
   <si>
     <t xml:space="preserve">Waiting for Carrier to send the package to Buyer. Your payout will be disbursed after Buyer receive the package.</t>
   </si>
   <si>
-    <t xml:space="preserve">Please set your Bank Account details on your Profile/ Credentials. Wait for Buyer prefered couried detail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clicked on "Send Prefered Courier"</t>
+    <t xml:space="preserve">Please wait for Buyer to send his/her Preferred Courier data before you send Reshipment cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clicked on "Save Prefered Courier"</t>
   </si>
   <si>
     <t xml:space="preserve">Prefered courier sent. Wait for Reshipment Cost.</t>
@@ -300,7 +298,7 @@
     <t xml:space="preserve">Reshipment Cost sent. Wait for Buyer's transfer proof</t>
   </si>
   <si>
-    <t xml:space="preserve">Clicked on "Send Transfer Proof"</t>
+    <t xml:space="preserve">Clicked on "Upload Transfer Proof"</t>
   </si>
   <si>
     <t xml:space="preserve">Transfer Proof sent. Wait for Airway Bill.</t>
@@ -324,28 +322,31 @@
     <t>15.1</t>
   </si>
   <si>
+    <t xml:space="preserve">You confirmed have reviewed and received the package on &lt;date, time&gt;. Transaction closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package received confirmed by the Buyer. Your payout will be disbursed within 24 hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUYER SELECTED: PICKUP THE PACKAGE</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom Duty Paid. Check Chat Box to see the time set by Carrier to visit Carrier location.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for Buyer to collect the package. Your payout will be disbursed after Buyer receive the package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customs Duty paid. Use Chat Box to inform Buyer for the time to visit collecting the package.</t>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
     <t xml:space="preserve">You have reviewed and received the package. Transaction closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Package received by the Buyer. Your payout will be disbursed within 24 hours.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUYER SELECTED: PICKUP THE PACKAGE</t>
-  </si>
-  <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Custom Duty Paid. Check Chat Box to see the time set by Carrier to visit Carrier location.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for Buyer to collect the package. Your payout will be disbursed after Buyer receive the package.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customs Duty paid. Use Chat Box to inform Buyer for the time to visit collecting the package.</t>
-  </si>
-  <si>
-    <t>15.2</t>
   </si>
   <si>
     <t xml:space="preserve">Package collected by the Buyer. Your payout will be disbursed within 24 hours.</t>
@@ -373,7 +374,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,8 +399,14 @@
         <bgColor indexed="5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor theme="5" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -411,43 +418,6 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -472,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,50 +463,78 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1042,6 +1040,7 @@
     <col customWidth="1" min="3" max="3" width="7.7109375"/>
     <col customWidth="1" min="4" max="4" style="2" width="20.7109375"/>
     <col customWidth="1" min="5" max="7" width="26.7109375"/>
+    <col customWidth="1" min="12" max="14" width="30.57421875"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -1203,10 +1202,10 @@
       <c r="D9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="12" t="s">
@@ -1217,23 +1216,32 @@
       <c r="A10" s="9">
         <v>4</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="L10" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="M10" s="17" t="s">
         <v>32</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="128.25">
@@ -1272,7 +1280,7 @@
       <c r="D12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="14" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="11" t="s">
@@ -1286,7 +1294,7 @@
       <c r="A13" s="9">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1295,13 +1303,13 @@
       <c r="D13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1309,7 +1317,7 @@
       <c r="A14" s="9">
         <v>5</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -1318,13 +1326,13 @@
       <c r="D14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1332,7 +1340,7 @@
       <c r="A15" s="9">
         <v>6</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -1341,60 +1349,60 @@
       <c r="D15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>56</v>
+      <c r="G15" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="16" ht="142.5">
       <c r="A16" s="9">
         <v>6</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>57</v>
+      <c r="B16" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="G16" s="14" t="s">
         <v>59</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" ht="71.25">
       <c r="A17" s="9">
         <v>7</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="18">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="G17" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="18" ht="14.25">
@@ -1408,7 +1416,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1418,61 +1426,66 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20"/>
-      <c r="D20"/>
-    </row>
-    <row r="21" ht="71.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" ht="99.75">
       <c r="A21" s="9">
         <v>8</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>67</v>
+      <c r="B21" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" ht="71.25">
       <c r="A22" s="9">
         <v>8</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>69</v>
+      <c r="B22" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="F22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="G22" s="24" t="s">
         <v>72</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="23" ht="71.25">
       <c r="A23" s="9">
         <v>9</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>74</v>
+      <c r="B23" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>6</v>
@@ -1481,21 +1494,21 @@
         <v>43</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="24" ht="42.75">
       <c r="A24" s="9">
         <v>9</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>78</v>
+      <c r="B24" s="18" t="s">
+        <v>77</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>47</v>
@@ -1503,167 +1516,181 @@
       <c r="D24" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="12" t="s">
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="26"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="16" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="26"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" ht="57">
+      <c r="A28" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="1"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" ht="57">
-      <c r="A28" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>83</v>
+      <c r="B28" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="F28" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="G28" s="29" t="s">
         <v>86</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="29" ht="57">
       <c r="A29" s="9">
         <v>11</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="18">
         <v>11</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="F29" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="30" ht="57">
       <c r="A30" s="9">
         <v>12</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="18">
         <v>12</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="F30" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="31" ht="57">
       <c r="A31" s="9">
         <v>13</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="18">
         <v>13</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="F31" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="32" ht="57">
       <c r="A32" s="9">
         <v>14</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="18">
         <v>14</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="F32" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="G32" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="12" t="s">
+    </row>
+    <row r="33" ht="57">
+      <c r="A33" s="9" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" ht="42.75">
-      <c r="A33" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>101</v>
+      <c r="B33" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F33" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>103</v>
+      <c r="G33" s="22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="34" ht="14.25">
@@ -1671,56 +1698,68 @@
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="10"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="26"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" ht="57">
+      <c r="A37" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="37" ht="57">
-      <c r="A37" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>105</v>
+      <c r="B37" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E37" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="G37" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G37" s="12" t="s">
+    </row>
+    <row r="38" ht="42.75">
+      <c r="A38" s="26" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="38" ht="42.75">
-      <c r="A38" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>109</v>
+      <c r="B38" s="26" t="s">
+        <v>108</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>110</v>
@@ -1730,13 +1769,13 @@
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
+++ b/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t xml:space="preserve">USERS AND SYSTEM STEPS RELATIONSHIP</t>
   </si>
@@ -326,6 +326,15 @@
   </si>
   <si>
     <t xml:space="preserve">Package received confirmed by the Buyer. Your payout will be disbursed within 24 hours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Process Payout Disbursements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For your record, Carrier and Proxy Buyer payouts have been disbursed on &lt;date, time&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your payout has been processed on &lt;date, time&gt;. Thank you for doing business with ProxyBuying</t>
   </si>
   <si>
     <t xml:space="preserve">BUYER SELECTED: PICKUP THE PACKAGE</t>
@@ -442,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -526,6 +535,9 @@
     </xf>
     <xf fontId="1" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1693,89 +1705,112 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" ht="14.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
+    <row r="34" ht="57">
+      <c r="A34" s="9">
+        <v>16</v>
+      </c>
+      <c r="B34" s="18">
+        <v>16</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-    </row>
-    <row r="37" ht="57">
-      <c r="A37" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="A36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="26"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" ht="57">
+      <c r="A38" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D38" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" ht="42.75">
-      <c r="A38" s="26" t="s">
+      <c r="E38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="12" t="s">
+      <c r="F38" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>110</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" ht="14.25">
-      <c r="A39" s="31"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
+    <row r="39" ht="42.75">
+      <c r="A39" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="32"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1786,7 +1821,7 @@
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
+++ b/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
@@ -355,7 +355,7 @@
     <t>15.2</t>
   </si>
   <si>
-    <t xml:space="preserve">You have reviewed and received the package. Transaction closed</t>
+    <t xml:space="preserve">You have reviewed and received the package on &lt;date, time&gt;. Transaction closed</t>
   </si>
   <si>
     <t xml:space="preserve">Package collected by the Buyer. Your payout will be disbursed within 24 hours.</t>
@@ -1780,11 +1780,11 @@
         <v>110</v>
       </c>
     </row>
-    <row r="39" ht="42.75">
-      <c r="A39" s="26" t="s">
+    <row r="39" ht="57">
+      <c r="A39" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="9" t="s">
         <v>111</v>
       </c>
       <c r="C39" s="9" t="s">
@@ -1793,7 +1793,7 @@
       <c r="D39" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="22" t="s">
         <v>112</v>
       </c>
       <c r="F39" s="12" t="s">

--- a/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
+++ b/proxybuying-obsidian/AI-Context/references/UserAndSystemStepsRelationship.xlsx
@@ -6,7 +6,7 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -15,6 +15,37 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={CFFA49ED-4450-354E-22CF-5ACF75A6C676}</author>
+  </authors>
+  <commentList>
+    <comment ref="E8" authorId="0" xr:uid="{CFFA49ED-4450-354E-22CF-5ACF75A6C676}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>opa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Update wordings
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
@@ -78,7 +109,7 @@
     <t xml:space="preserve">Clicked on "Process Estimate" button on "Action" column on "My Proxy Buying" table</t>
   </si>
   <si>
-    <t xml:space="preserve">Please fill in all required data. After you click "Send Estimate" Buyer will be notified.</t>
+    <t xml:space="preserve">Please fill in all required data. After you click "Send Estimate" Buyer will be notified. Use the Chat Box to discuss with Buyer on ordered products issues (out-of-stock, shortage quantity, etc.)</t>
   </si>
   <si>
     <t>2.2</t>
@@ -87,7 +118,7 @@
     <t xml:space="preserve">Clicked on "Send Estimate"</t>
   </si>
   <si>
-    <t xml:space="preserve">Proxy Buyer has sent the estimate. Please Accept or Reject it. Use the Chat Box if you want to negotiate the Margin with Proxy Buyer.</t>
+    <t xml:space="preserve">Proxy Buyer has sent the estimate. Please Accept, Edit, or Reject it. Editing your order sends it back to the Proxy Buyer to re-estimate. Use the Chat Box if you want to negotiate the Margin with Proxy Buyer.</t>
   </si>
   <si>
     <t xml:space="preserve">Estimate Sent, waiting for Buyer to Accept it. Use the Chat Box to check if Buyer is asking to negotiate the Margin. You still be able to edit the Margin before Buyer Accepting or Rejecting your estimate.</t>
@@ -451,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="30">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,11 +524,8 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -505,16 +533,7 @@
     <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
@@ -535,9 +554,6 @@
     </xf>
     <xf fontId="1" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,6 +580,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="opa" id="{8DC25E0B-C16D-9521-27F4-677E169D6E97}" userId="opa" providerId="Teamlab"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1044,6 +1066,15 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E8" dT="2026-07-06T03:30:59.03Z" personId="{8DC25E0B-C16D-9521-27F4-677E169D6E97}" id="{CFFA49ED-4450-354E-22CF-5ACF75A6C676}" done="1">
+    <text xml:space="preserve">Update wordings
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1155,7 +1186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="71.25">
+    <row r="7" ht="99.75">
       <c r="A7" s="9">
         <v>2</v>
       </c>
@@ -1191,10 +1222,10 @@
       <c r="D8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="12" t="s">
@@ -1214,10 +1245,10 @@
       <c r="D9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="13" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="12" t="s">
@@ -1234,25 +1265,25 @@
       <c r="C10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1292,7 +1323,7 @@
       <c r="D12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="F12" s="11" t="s">
@@ -1306,7 +1337,7 @@
       <c r="A13" s="9">
         <v>5</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1315,13 +1346,13 @@
       <c r="D13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1329,7 +1360,7 @@
       <c r="A14" s="9">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="17" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -1338,13 +1369,13 @@
       <c r="D14" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="13" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1352,7 +1383,7 @@
       <c r="A15" s="9">
         <v>6</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -1361,7 +1392,7 @@
       <c r="D15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="18" t="s">
         <v>49</v>
       </c>
       <c r="F15" s="11" t="s">
@@ -1375,7 +1406,7 @@
       <c r="A16" s="9">
         <v>6</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C16" s="10" t="s">
@@ -1384,13 +1415,13 @@
       <c r="D16" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="11" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1398,7 +1429,7 @@
       <c r="A17" s="9">
         <v>7</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -1407,10 +1438,10 @@
       <c r="D17" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="18" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="13" t="s">
@@ -1438,19 +1469,19 @@
       <c r="G19" s="6"/>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" ht="99.75">
       <c r="A21" s="9">
         <v>8</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>65</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -1459,13 +1490,13 @@
       <c r="D21" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1473,7 +1504,7 @@
       <c r="A22" s="9">
         <v>8</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C22" s="9" t="s">
@@ -1482,13 +1513,13 @@
       <c r="D22" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="12" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="20" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1496,7 +1527,7 @@
       <c r="A23" s="9">
         <v>9</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="9" t="s">
@@ -1519,7 +1550,7 @@
       <c r="A24" s="9">
         <v>9</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C24" s="9" t="s">
@@ -1528,24 +1559,24 @@
       <c r="D24" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="G24" s="21" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="6" t="s">
@@ -1559,19 +1590,19 @@
       <c r="G26" s="6"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" ht="57">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="17" t="s">
         <v>82</v>
       </c>
       <c r="C28" s="9" t="s">
@@ -1580,13 +1611,13 @@
       <c r="D28" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="25" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1594,13 +1625,13 @@
       <c r="A29" s="9">
         <v>11</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="17">
         <v>11</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="10" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -1617,7 +1648,7 @@
       <c r="A30" s="9">
         <v>12</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="17">
         <v>12</v>
       </c>
       <c r="C30" s="9" t="s">
@@ -1640,13 +1671,13 @@
       <c r="A31" s="9">
         <v>13</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="17">
         <v>13</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="10" t="s">
         <v>93</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -1663,7 +1694,7 @@
       <c r="A32" s="9">
         <v>14</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="17">
         <v>14</v>
       </c>
       <c r="C32" s="9" t="s">
@@ -1686,7 +1717,7 @@
       <c r="A33" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="17" t="s">
         <v>100</v>
       </c>
       <c r="C33" s="9" t="s">
@@ -1695,13 +1726,13 @@
       <c r="D33" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="12" t="s">
         <v>101</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="12" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1709,22 +1740,22 @@
       <c r="A34" s="9">
         <v>16</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>16</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="12" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1733,9 +1764,9 @@
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="10"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="6" t="s">
@@ -1749,19 +1780,19 @@
       <c r="G36" s="6"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" ht="57">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="26" t="s">
         <v>107</v>
       </c>
       <c r="C38" s="9" t="s">
@@ -1793,7 +1824,7 @@
       <c r="D39" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="12" t="s">
         <v>112</v>
       </c>
       <c r="F39" s="12" t="s">
@@ -1804,13 +1835,13 @@
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="32"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1827,5 +1858,6 @@
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>